--- a/source/bin/excel/mail.xlsx
+++ b/source/bin/excel/mail.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122ABE18-2E32-489B-9C82-8B0C1F0160E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED14941-2944-4009-80E7-71155B98FF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="385">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -9903,12 +9903,697 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>万事屋一姬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>万事屋一姬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动奖励</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>萬事屋一姬活動獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ichihime's Odd Jobs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Event Rewards</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해결사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이치히메</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>感谢参与</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>万事屋一姬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动，请查收您的奖励。
+邮件有效期为30天，请注意及时领取。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>感謝參與</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>萬事屋一姬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thank you for participating in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ichihime's Odd Jobs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> event. Please claim your rewards.
+*Upon receiving the mail, it will expire in 30 days. Please claim it in time.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해결사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이치히메</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참가해주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작사님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감사의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우편의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유효기간은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>よろず屋 一姫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」報酬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
+イベント「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>よろず屋 一姫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」の報酬をお送りいたしました。
+これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
+※本メールは受信後、30日で削除されますのでご注意ください。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="44" x14ac:knownFonts="1">
+  <fonts count="47" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10235,6 +10920,29 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -10288,7 +10996,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -10348,6 +11056,7 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -10697,7 +11406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -12041,6 +12750,50 @@
         <v>108</v>
       </c>
     </row>
+    <row r="35" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>374</v>
+      </c>
+      <c r="B35">
+        <v>132</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="F35" t="s">
+        <v>383</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="H35" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="J35" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="K35" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="L35" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="M35" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="N35" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/source/bin/excel/mail.xlsx
+++ b/source/bin/excel/mail.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED14941-2944-4009-80E7-71155B98FF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B2F5F9-C038-410C-9623-486790D3CF63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="407">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -10585,6 +10585,1385 @@
       <t>」の報酬をお送りいたしました。
 これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
 ※本メールは受信後、30日で削除されますのでご注意ください。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>雪球大作战</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动奖励</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪球大作戰活動獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tbd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」報酬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">tbd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Event Rewards</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>tbd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>感谢参与</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>雪球大作战</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动，请查收您的奖励。
+邮件有效期为30天，请注意及时领取。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
+イベント「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tbd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」の報酬をお送りいたしました。
+これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
+※本メールは受信後、30日で削除されますのでご注意ください。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thank you for participating in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tbd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> event. Please claim your rewards.
+*Upon receiving the mail, it will expire in 30 days. Please claim it in time.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>tbd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참가해주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작사님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감사의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우편의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유효기간은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪球大作战</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>感謝參與</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>雪球大作戰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超级麻将牌宾果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>超级麻将牌宾果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动奖励</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超級麻將牌賓果活動獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スーパーマージャンビンゴ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」報酬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Super Mahjong Bingo</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Event Rewards</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슈퍼</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마작패</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빙고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>感谢参与</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>超级麻将牌宾果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动，请查收您的奖励。
+邮件有效期为30天，请注意及时领取。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>感謝參與</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>超級麻將牌賓果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
+イベント「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スーパーマージャンビンゴ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」の報酬をお送りいたしました。
+これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
+※本メールは受信後、30日で削除されますのでご注意ください。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thank you for participating in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Super Mahjong Bingo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> event. Please claim your rewards.
+*Upon receiving the mail, it will expire in 30 days. Please claim it in time.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슈퍼</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마작패</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빙고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참가해주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작사님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감사의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우편의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유효기간은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -11406,7 +12785,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -12794,6 +14173,94 @@
         <v>108</v>
       </c>
     </row>
+    <row r="36" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>396</v>
+      </c>
+      <c r="B36">
+        <v>133</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="F36" t="s">
+        <v>399</v>
+      </c>
+      <c r="G36" t="s">
+        <v>400</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="J36" s="23" t="s">
+        <v>402</v>
+      </c>
+      <c r="K36" s="23" t="s">
+        <v>403</v>
+      </c>
+      <c r="L36" s="23" t="s">
+        <v>404</v>
+      </c>
+      <c r="M36" s="23" t="s">
+        <v>405</v>
+      </c>
+      <c r="N36" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="O36">
+        <v>1</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>394</v>
+      </c>
+      <c r="B37">
+        <v>134</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="F37" t="s">
+        <v>387</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="H37" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="J37" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="K37" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="L37" s="23" t="s">
+        <v>391</v>
+      </c>
+      <c r="M37" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="N37" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/source/bin/excel/mail.xlsx
+++ b/source/bin/excel/mail.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B2F5F9-C038-410C-9623-486790D3CF63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DEFDC0-A2ED-4264-B416-01E1540963C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="418">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -10619,110 +10619,6 @@
   </si>
   <si>
     <r>
-      <t>「</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tbd</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>」報酬</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">tbd </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Event Rewards</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>tbd</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Batang"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이벤트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Batang"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보상</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>感谢参与</t>
     </r>
     <r>
@@ -10752,6 +10648,291 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>雪球大作战</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>感謝參與</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>雪球大作戰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超级麻将牌宾果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>超级麻将牌宾果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动奖励</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超級麻將牌賓果活動獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>スーパーマージャンビンゴ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」報酬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Super Mahjong Bingo</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Event Rewards</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슈퍼</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마작패</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빙고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>感谢参与</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>超级麻将牌宾果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动，请查收您的奖励。
+邮件有效期为30天，请注意及时领取。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>感謝參與</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>超級麻將牌賓果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
 イベント「</t>
@@ -10766,7 +10947,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>tbd</t>
+      <t>スーパーマージャンビンゴ</t>
     </r>
     <r>
       <rPr>
@@ -10797,7 +10978,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>tbd</t>
+      <t>Super Mahjong Bingo</t>
     </r>
     <r>
       <rPr>
@@ -10819,10 +11000,53 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슈퍼</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="3"/>
       </rPr>
-      <t>tbd</t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마작패</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빙고</t>
     </r>
     <r>
       <rPr>
@@ -11196,55 +11420,20 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>雪球大作战</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>感謝參與</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>雪球大作戰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>活動，請查收您的獎勵。
-郵件有效期為30天，請注意及時領取。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>超级麻将牌宾果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>超级麻将牌宾果</t>
+    <r>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>雪玉ファイター！</t>
     </r>
     <r>
       <rPr>
@@ -11254,29 +11443,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>活动奖励</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>超級麻將牌賓果活動獎勵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>「</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>スーパーマージャンビンゴ</t>
+      <t>」報酬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Snowball Brawl </t>
     </r>
     <r>
       <rPr>
@@ -11286,57 +11468,94 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>」報酬</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
+      <t>Event Rewards</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Super Mahjong Bingo</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈덩이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Event Rewards</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Malgun Gothic"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>슈퍼</t>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대난투</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈덩이</t>
     </r>
     <r>
       <rPr>
@@ -11344,7 +11563,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
-        <family val="1"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -11354,129 +11573,409 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Malgun Gothic"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마작패</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빙고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Batang"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이벤트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Batang"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보상</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>感谢参与</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>超级麻将牌宾果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>活动，请查收您的奖励。
-邮件有效期为30天，请注意及时领取。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>感謝參與</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>超級麻將牌賓果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>活動，請查收您的獎勵。
-郵件有效期為30天，請注意及時領取。</t>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대난투</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참가해주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작사님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감사의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우편의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유효기간은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thank you for participating in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Snowball Brawl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> event. Please claim your rewards.
+*Upon receiving the mail, it will expire in 30 days. Please claim it in time.</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -11495,7 +11994,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>スーパーマージャンビンゴ</t>
+      <t>雪玉ファイター！</t>
     </r>
     <r>
       <rPr>
@@ -11513,6 +12012,164 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>米亚的直播间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>米亚的直播间活动奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>米亞的直播間活動獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tbd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」報酬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">tbd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Event Rewards</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>tbd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感谢参与米亚的直播间活动，请查收您的奖励。
+邮件有效期为30天，请注意及时领取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感謝參與米亞的直播間活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
+イベント「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tbd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」の報酬をお送りいたしました。
+これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
+※本メールは受信後、30日で削除されますのでご注意ください。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Thank you for participating in the </t>
     </r>
@@ -11526,7 +12183,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Super Mahjong Bingo</t>
+      <t>tbd</t>
     </r>
     <r>
       <rPr>
@@ -11548,53 +12205,10 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>슈퍼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="3"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마작패</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빙고</t>
+      <t>tbd</t>
     </r>
     <r>
       <rPr>
@@ -11972,7 +12586,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="47" x14ac:knownFonts="1">
+  <fonts count="47">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12722,7 +13336,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.375" bestFit="1" customWidth="1"/>
@@ -12733,7 +13347,7 @@
     <col min="8" max="8" width="55.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -12750,7 +13364,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -12785,8 +13399,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S37"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:S38"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
@@ -12806,7 +13420,7 @@
     <col min="17" max="19" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -12865,7 +13479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -12888,7 +13502,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -12941,7 +13555,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19">
       <c r="B4">
         <v>101</v>
       </c>
@@ -12955,7 +13569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19">
       <c r="B5">
         <v>102</v>
       </c>
@@ -12969,7 +13583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19">
       <c r="B6">
         <v>103</v>
       </c>
@@ -12983,7 +13597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19">
       <c r="B7">
         <v>104</v>
       </c>
@@ -12997,7 +13611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="171" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="171">
       <c r="B8">
         <v>105</v>
       </c>
@@ -13017,7 +13631,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="71.25">
       <c r="B9">
         <v>106</v>
       </c>
@@ -13053,7 +13667,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="185.25">
       <c r="B10">
         <v>107</v>
       </c>
@@ -13089,7 +13703,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="71.25">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -13128,7 +13742,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="140.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="140.25">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -13172,7 +13786,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="140.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="140.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -13216,7 +13830,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="85.5">
       <c r="A14" t="s">
         <v>148</v>
       </c>
@@ -13248,7 +13862,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="140.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="140.25">
       <c r="A15" t="s">
         <v>152</v>
       </c>
@@ -13292,7 +13906,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="51">
       <c r="A16" t="s">
         <v>164</v>
       </c>
@@ -13336,7 +13950,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="141" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="141" thickBot="1">
       <c r="A17" t="s">
         <v>175</v>
       </c>
@@ -13380,7 +13994,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="51.75" thickBot="1">
       <c r="A18" t="s">
         <v>185</v>
       </c>
@@ -13424,7 +14038,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" ht="141" thickBot="1">
       <c r="A19" s="8" t="s">
         <v>194</v>
       </c>
@@ -13468,7 +14082,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" ht="52.5" customHeight="1" thickBot="1">
       <c r="A20" t="s">
         <v>202</v>
       </c>
@@ -13512,7 +14126,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="45.75" customHeight="1" thickBot="1">
       <c r="A21" t="s">
         <v>215</v>
       </c>
@@ -13556,7 +14170,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" ht="45.75" customHeight="1" thickBot="1">
       <c r="A22" t="s">
         <v>224</v>
       </c>
@@ -13600,7 +14214,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" ht="45.75" customHeight="1" thickBot="1">
       <c r="A23" t="s">
         <v>225</v>
       </c>
@@ -13644,7 +14258,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" ht="54.75" customHeight="1" thickBot="1">
       <c r="A24" t="s">
         <v>251</v>
       </c>
@@ -13688,7 +14302,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" ht="55.5" customHeight="1" thickBot="1">
       <c r="A25" t="s">
         <v>262</v>
       </c>
@@ -13732,7 +14346,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="54.75" customHeight="1" thickBot="1">
       <c r="A26" t="s">
         <v>273</v>
       </c>
@@ -13777,7 +14391,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="157.5" thickBot="1">
       <c r="A27" t="s">
         <v>285</v>
       </c>
@@ -13821,7 +14435,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="161.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" ht="161.25" thickBot="1">
       <c r="A28" t="s">
         <v>286</v>
       </c>
@@ -13865,7 +14479,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" ht="157.5" thickBot="1">
       <c r="A29" t="s">
         <v>308</v>
       </c>
@@ -13909,7 +14523,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" ht="157.5" thickBot="1">
       <c r="A30" t="s">
         <v>319</v>
       </c>
@@ -13953,7 +14567,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" ht="157.5" thickBot="1">
       <c r="A31" t="s">
         <v>330</v>
       </c>
@@ -13997,7 +14611,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="157.5" thickBot="1">
       <c r="A32" t="s">
         <v>341</v>
       </c>
@@ -14041,7 +14655,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" ht="157.5" thickBot="1">
       <c r="A33" t="s">
         <v>352</v>
       </c>
@@ -14085,7 +14699,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" ht="157.5" thickBot="1">
       <c r="A34" t="s">
         <v>363</v>
       </c>
@@ -14129,7 +14743,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" ht="157.5" thickBot="1">
       <c r="A35" t="s">
         <v>374</v>
       </c>
@@ -14173,42 +14787,42 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" ht="157.5" thickBot="1">
       <c r="A36" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B36">
         <v>133</v>
       </c>
       <c r="D36" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="F36" t="s">
+        <v>393</v>
+      </c>
+      <c r="G36" t="s">
+        <v>394</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="J36" s="23" t="s">
+        <v>396</v>
+      </c>
+      <c r="K36" s="23" t="s">
         <v>397</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="L36" s="23" t="s">
         <v>398</v>
       </c>
-      <c r="F36" t="s">
+      <c r="M36" s="23" t="s">
         <v>399</v>
       </c>
-      <c r="G36" t="s">
+      <c r="N36" s="24" t="s">
         <v>400</v>
-      </c>
-      <c r="H36" s="16" t="s">
-        <v>401</v>
-      </c>
-      <c r="J36" s="23" t="s">
-        <v>402</v>
-      </c>
-      <c r="K36" s="23" t="s">
-        <v>403</v>
-      </c>
-      <c r="L36" s="23" t="s">
-        <v>404</v>
-      </c>
-      <c r="M36" s="23" t="s">
-        <v>405</v>
-      </c>
-      <c r="N36" s="24" t="s">
-        <v>406</v>
       </c>
       <c r="O36">
         <v>1</v>
@@ -14217,9 +14831,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="157.5" thickBot="1">
       <c r="A37" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B37">
         <v>134</v>
@@ -14231,33 +14845,77 @@
         <v>386</v>
       </c>
       <c r="F37" t="s">
+        <v>401</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="H37" s="25" t="s">
+        <v>403</v>
+      </c>
+      <c r="J37" s="23" t="s">
         <v>387</v>
       </c>
-      <c r="G37" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="H37" s="25" t="s">
+      <c r="K37" s="23" t="s">
         <v>389</v>
       </c>
-      <c r="J37" s="23" t="s">
-        <v>390</v>
-      </c>
-      <c r="K37" s="23" t="s">
-        <v>395</v>
-      </c>
       <c r="L37" s="23" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="M37" s="23" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="N37" s="24" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="O37">
         <v>1</v>
       </c>
       <c r="P37" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="157.5" thickBot="1">
+      <c r="A38" t="s">
+        <v>407</v>
+      </c>
+      <c r="B38">
+        <v>135</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="F38" t="s">
+        <v>410</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="H38" s="25" t="s">
+        <v>412</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="L38" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="M38" s="23" t="s">
+        <v>416</v>
+      </c>
+      <c r="N38" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="O38">
+        <v>1</v>
+      </c>
+      <c r="P38" s="2" t="s">
         <v>108</v>
       </c>
     </row>
@@ -14271,7 +14929,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B3:N10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="21.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.125" customWidth="1"/>
@@ -14280,7 +14938,7 @@
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:14">
       <c r="B3" t="s">
         <v>22</v>
       </c>
@@ -14300,7 +14958,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:14">
       <c r="B4">
         <v>0</v>
       </c>
@@ -14329,7 +14987,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:14">
       <c r="B5">
         <v>1</v>
       </c>
@@ -14364,7 +15022,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:14">
       <c r="B6">
         <v>2</v>
       </c>
@@ -14398,7 +15056,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:14">
       <c r="I7" t="s">
         <v>59</v>
       </c>
@@ -14412,7 +15070,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:14">
       <c r="I8" t="s">
         <v>64</v>
       </c>
@@ -14426,7 +15084,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:14">
       <c r="I9" t="s">
         <v>68</v>
       </c>
@@ -14446,7 +15104,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:14">
       <c r="I10" t="s">
         <v>74</v>
       </c>

--- a/source/bin/excel/mail.xlsx
+++ b/source/bin/excel/mail.xlsx
@@ -1,37 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DEFDC0-A2ED-4264-B416-01E1540963C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C34FE73-9C3A-4EF2-9AB9-B6FAD78DA823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
     <sheet name="mail_template" sheetId="1" r:id="rId2"/>
     <sheet name="邮件参数" sheetId="7" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="449">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -12581,12 +12572,607 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>小黑盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>twitch drops</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Twitch drops验证码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Twitch drops驗證碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>您的小黑盒验证码为：${code}，此验证码用于小黑盒账户绑定，验证码有效期30分钟。
+如有任何疑问请联络客服邮箱：cs@maj-soul.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>您的小黑盒驗證碼為：${code}，此驗證碼用於小黑盒帳戶綁定，驗證碼有效期限30分鐘。
+如有任何疑問請聯絡客服信箱：cs@maj-soul.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小黑盒账号绑定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小黑盒帳號綁定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（CH-dev）Twitch drops绑定成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（CHST-dev）Twitch drops绑定成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（JP-dev）Twitch drops绑定成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（EN-dev）Twitch drops绑定成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（KR-dev）Twitch drops绑定成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神驰集愿训练度奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神驰集愿奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感谢参与神驰集愿活动，请查收您的奖励。
+邮件有效期为30天，请注意及时领取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感謝參與神馳集願活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神驰集愿活动训练度奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神馳集願活動訓練度獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「午神の願い事集め」イベントアイテム「練度」補填について</t>
+  </si>
+  <si>
+    <t>Wishes Unbridled: Gallop Power Rewards</t>
+  </si>
+  <si>
+    <t>소원이 닿는 곳 이벤트 훈련도 보상</t>
+  </si>
+  <si>
+    <t>「午神の願い事集め」イベントアイテム「ニンジン」補填について</t>
+  </si>
+  <si>
+    <t>Wishes Unbridled: Carrot Rewards</t>
+  </si>
+  <si>
+    <t>소원이 닿는 곳 이벤트 당근 보상</t>
+  </si>
+  <si>
+    <r>
+      <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
+イベント「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>午神の願い事集め</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」の報酬をお送りいたしました。
+これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
+※本メールは受信後、30日で削除されますのでご注意ください。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thank you for participating in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Wishes Unbridled</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> event. Please claim your rewards.
+*Upon receiving the mail, it will expire in 30 days. Please claim it in time.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소원이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>닿는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>곳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참가해주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작사님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감사의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우편의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유효기간은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神驰集愿活动胡萝卜收集奖励</t>
+  </si>
+  <si>
+    <t>神馳集願活動胡蘿蔔蒐集獎勵</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="47">
+  <fonts count="47" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12937,7 +13523,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -12950,8 +13536,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -12985,11 +13577,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -13050,6 +13657,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -13336,7 +13953,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.375" bestFit="1" customWidth="1"/>
@@ -13347,7 +13964,7 @@
     <col min="8" max="8" width="55.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -13364,7 +13981,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -13399,8 +14016,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S38"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:S42"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
@@ -13420,7 +14037,7 @@
     <col min="17" max="19" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -13479,7 +14096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -13502,7 +14119,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -13555,7 +14172,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>101</v>
       </c>
@@ -13569,7 +14186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>102</v>
       </c>
@@ -13583,7 +14200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>103</v>
       </c>
@@ -13597,7 +14214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>104</v>
       </c>
@@ -13611,7 +14228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="171">
+    <row r="8" spans="1:19" ht="171" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>105</v>
       </c>
@@ -13631,7 +14248,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="71.25">
+    <row r="9" spans="1:19" ht="71.25" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>106</v>
       </c>
@@ -13667,7 +14284,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="185.25">
+    <row r="10" spans="1:19" ht="185.25" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>107</v>
       </c>
@@ -13703,7 +14320,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="71.25">
+    <row r="11" spans="1:19" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -13742,7 +14359,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="140.25">
+    <row r="12" spans="1:19" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -13786,7 +14403,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="140.25">
+    <row r="13" spans="1:19" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -13830,7 +14447,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="85.5">
+    <row r="14" spans="1:19" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>148</v>
       </c>
@@ -13862,7 +14479,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="140.25">
+    <row r="15" spans="1:19" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>152</v>
       </c>
@@ -13906,7 +14523,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="51">
+    <row r="16" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>164</v>
       </c>
@@ -13950,7 +14567,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="141" thickBot="1">
+    <row r="17" spans="1:16" ht="141" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>175</v>
       </c>
@@ -13994,7 +14611,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="51.75" thickBot="1">
+    <row r="18" spans="1:16" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>185</v>
       </c>
@@ -14038,7 +14655,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="141" thickBot="1">
+    <row r="19" spans="1:16" ht="141" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>194</v>
       </c>
@@ -14082,7 +14699,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="52.5" customHeight="1" thickBot="1">
+    <row r="20" spans="1:16" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>202</v>
       </c>
@@ -14126,7 +14743,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="45.75" customHeight="1" thickBot="1">
+    <row r="21" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>215</v>
       </c>
@@ -14170,7 +14787,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="45.75" customHeight="1" thickBot="1">
+    <row r="22" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>224</v>
       </c>
@@ -14214,7 +14831,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="45.75" customHeight="1" thickBot="1">
+    <row r="23" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>225</v>
       </c>
@@ -14258,7 +14875,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="54.75" customHeight="1" thickBot="1">
+    <row r="24" spans="1:16" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>251</v>
       </c>
@@ -14302,7 +14919,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="55.5" customHeight="1" thickBot="1">
+    <row r="25" spans="1:16" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>262</v>
       </c>
@@ -14346,7 +14963,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="54.75" customHeight="1" thickBot="1">
+    <row r="26" spans="1:16" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>273</v>
       </c>
@@ -14391,7 +15008,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="157.5" thickBot="1">
+    <row r="27" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>285</v>
       </c>
@@ -14435,7 +15052,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="161.25" thickBot="1">
+    <row r="28" spans="1:16" ht="161.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>286</v>
       </c>
@@ -14479,7 +15096,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="157.5" thickBot="1">
+    <row r="29" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>308</v>
       </c>
@@ -14523,7 +15140,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="157.5" thickBot="1">
+    <row r="30" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>319</v>
       </c>
@@ -14567,7 +15184,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="157.5" thickBot="1">
+    <row r="31" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>330</v>
       </c>
@@ -14611,7 +15228,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="157.5" thickBot="1">
+    <row r="32" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>341</v>
       </c>
@@ -14655,7 +15272,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="157.5" thickBot="1">
+    <row r="33" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>352</v>
       </c>
@@ -14699,7 +15316,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="157.5" thickBot="1">
+    <row r="34" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>363</v>
       </c>
@@ -14743,7 +15360,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="157.5" thickBot="1">
+    <row r="35" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>374</v>
       </c>
@@ -14787,7 +15404,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="157.5" thickBot="1">
+    <row r="36" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>390</v>
       </c>
@@ -14831,7 +15448,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="157.5" thickBot="1">
+    <row r="37" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>388</v>
       </c>
@@ -14875,7 +15492,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="157.5" thickBot="1">
+    <row r="38" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>407</v>
       </c>
@@ -14916,6 +15533,155 @@
         <v>1</v>
       </c>
       <c r="P38" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A39" s="26" t="s">
+        <v>418</v>
+      </c>
+      <c r="B39">
+        <v>10001</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="J39" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="K39" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="26" t="s">
+        <v>419</v>
+      </c>
+      <c r="B40">
+        <v>10002</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="K40" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="L40" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="M40" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>431</v>
+      </c>
+      <c r="B41">
+        <v>136</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>438</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>439</v>
+      </c>
+      <c r="H41" s="28" t="s">
+        <v>440</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="L41" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="M41" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="N41" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>432</v>
+      </c>
+      <c r="B42">
+        <v>137</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>441</v>
+      </c>
+      <c r="G42" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="H42" s="28" t="s">
+        <v>443</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="K42" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="L42" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="M42" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="N42" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="P42" s="2" t="s">
         <v>108</v>
       </c>
     </row>
@@ -14929,7 +15695,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B3:N10"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="21.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.125" customWidth="1"/>
@@ -14938,7 +15704,7 @@
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>22</v>
       </c>
@@ -14958,7 +15724,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="2:14">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>0</v>
       </c>
@@ -14987,7 +15753,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="2:14">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -15022,7 +15788,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="2:14">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2</v>
       </c>
@@ -15056,7 +15822,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="2:14">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I7" t="s">
         <v>59</v>
       </c>
@@ -15070,7 +15836,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="2:14">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I8" t="s">
         <v>64</v>
       </c>
@@ -15084,7 +15850,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="2:14">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I9" t="s">
         <v>68</v>
       </c>
@@ -15104,7 +15870,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="2:14">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I10" t="s">
         <v>74</v>
       </c>

--- a/source/bin/excel/mail.xlsx
+++ b/source/bin/excel/mail.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C34FE73-9C3A-4EF2-9AB9-B6FAD78DA823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190B911E-05C8-482A-86A6-8C3E4A323585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="444">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -12015,6 +12015,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>感谢参与米亚的直播间活动，请查收您的奖励。
+邮件有效期为30天，请注意及时领取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感謝參與米亞的直播間活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>「</t>
     </r>
@@ -12028,7 +12038,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>tbd</t>
+      <t>ミアの配信にようこそ</t>
     </r>
     <r>
       <rPr>
@@ -12053,7 +12063,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">tbd </t>
+      <t xml:space="preserve">Mia's Channel </t>
     </r>
     <r>
       <rPr>
@@ -12068,6 +12078,17 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미야</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -12076,7 +12097,18 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>tbd</t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>채널</t>
     </r>
     <r>
       <rPr>
@@ -12116,16 +12148,6 @@
       </rPr>
       <t>보상</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>感谢参与米亚的直播间活动，请查收您的奖励。
-邮件有效期为30天，请注意及时领取。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>感謝參與米亞的直播間活動，請查收您的獎勵。
-郵件有效期為30天，請注意及時領取。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -12143,7 +12165,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>tbd</t>
+      <t>ミアの配信にようこそ</t>
     </r>
     <r>
       <rPr>
@@ -12174,7 +12196,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>tbd</t>
+      <t>Mia's Channel</t>
     </r>
     <r>
       <rPr>
@@ -12196,10 +12218,32 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미야</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="3"/>
       </rPr>
-      <t>tbd</t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>채널</t>
     </r>
     <r>
       <rPr>
@@ -12573,57 +12617,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>小黑盒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>twitch drops</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Twitch drops验证码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Twitch drops驗證碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>您的小黑盒验证码为：${code}，此验证码用于小黑盒账户绑定，验证码有效期30分钟。
-如有任何疑问请联络客服邮箱：cs@maj-soul.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>您的小黑盒驗證碼為：${code}，此驗證碼用於小黑盒帳戶綁定，驗證碼有效期限30分鐘。
-如有任何疑問請聯絡客服信箱：cs@maj-soul.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小黑盒账号绑定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小黑盒帳號綁定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>（CH-dev）Twitch drops绑定成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>（CHST-dev）Twitch drops绑定成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>（JP-dev）Twitch drops绑定成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>（EN-dev）Twitch drops绑定成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>（KR-dev）Twitch drops绑定成功</t>
+    <t>2d</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -12631,8 +12625,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>神驰集愿奖励</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>神驰集愿活动训练度奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神馳集願活動訓練度獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「午神の願い事集め」イベントアイテム「練度」補填について</t>
+  </si>
+  <si>
+    <t>Wishes Unbridled: Gallop Power Rewards</t>
+  </si>
+  <si>
+    <t>소원이 닿는 곳 이벤트 훈련도 보상</t>
   </si>
   <si>
     <t>感谢参与神驰集愿活动，请查收您的奖励。
@@ -12643,36 +12650,6 @@
     <t>感謝參與神馳集願活動，請查收您的獎勵。
 郵件有效期為30天，請注意及時領取。</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>神驰集愿活动训练度奖励</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>神馳集願活動訓練度獎勵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2d</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>「午神の願い事集め」イベントアイテム「練度」補填について</t>
-  </si>
-  <si>
-    <t>Wishes Unbridled: Gallop Power Rewards</t>
-  </si>
-  <si>
-    <t>소원이 닿는 곳 이벤트 훈련도 보상</t>
-  </si>
-  <si>
-    <t>「午神の願い事集め」イベントアイテム「ニンジン」補填について</t>
-  </si>
-  <si>
-    <t>Wishes Unbridled: Carrot Rewards</t>
-  </si>
-  <si>
-    <t>소원이 닿는 곳 이벤트 당근 보상</t>
   </si>
   <si>
     <r>
@@ -13162,10 +13139,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>神驰集愿奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>神驰集愿活动胡萝卜收集奖励</t>
   </si>
   <si>
     <t>神馳集願活動胡蘿蔔蒐集獎勵</t>
+  </si>
+  <si>
+    <t>「午神の願い事集め」イベントアイテム「ニンジン」補填について</t>
+  </si>
+  <si>
+    <t>Wishes Unbridled: Carrot Rewards</t>
+  </si>
+  <si>
+    <t>소원이 닿는 곳 이벤트 당근 보상</t>
+  </si>
+  <si>
+    <t>小黑盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小黑盒账号绑定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小黑盒帳號綁定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>您的小黑盒验证码为：${code}，此验证码用于小黑盒账户绑定，验证码有效期30分钟。
+如有任何疑问请联络客服邮箱：cs@maj-soul.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>您的小黑盒驗證碼為：${code}，此驗證碼用於小黑盒帳戶綁定，驗證碼有效期限30分鐘。
+如有任何疑問請聯絡客服信箱：cs@maj-soul.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Twitch Drops Rewards1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Twitch Drops Rewards2</t>
+  </si>
+  <si>
+    <t>Twitch Drops Rewards3</t>
   </si>
 </sst>
 </file>
@@ -13657,21 +13679,32 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -14016,10 +14049,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.125" customWidth="1"/>
+    <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.375" bestFit="1" customWidth="1"/>
@@ -15506,19 +15539,19 @@
         <v>409</v>
       </c>
       <c r="F38" t="s">
+        <v>412</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="H38" s="25" t="s">
+        <v>414</v>
+      </c>
+      <c r="J38" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="G38" s="17" t="s">
+      <c r="K38" s="10" t="s">
         <v>411</v>
-      </c>
-      <c r="H38" s="25" t="s">
-        <v>412</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="K38" s="10" t="s">
-        <v>414</v>
       </c>
       <c r="L38" s="23" t="s">
         <v>415</v>
@@ -15537,156 +15570,166 @@
       </c>
     </row>
     <row r="39" spans="1:16" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A39" s="26" t="s">
-        <v>418</v>
+      <c r="A39" s="28" t="s">
+        <v>436</v>
       </c>
       <c r="B39">
         <v>10001</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>425</v>
-      </c>
-      <c r="J39" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="K39" s="27" t="s">
-        <v>423</v>
+        <v>438</v>
+      </c>
+      <c r="J39" s="29" t="s">
+        <v>439</v>
+      </c>
+      <c r="K39" s="29" t="s">
+        <v>440</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="26" t="s">
-        <v>419</v>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" s="28" t="s">
+        <v>441</v>
       </c>
       <c r="B40">
         <v>10002</v>
       </c>
-      <c r="D40" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>421</v>
-      </c>
-      <c r="J40" s="17" t="s">
-        <v>426</v>
-      </c>
-      <c r="K40" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="L40" s="17" t="s">
-        <v>428</v>
-      </c>
-      <c r="M40" s="17" t="s">
-        <v>429</v>
-      </c>
-      <c r="N40" s="17" t="s">
-        <v>430</v>
-      </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>431</v>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A41" s="28" t="s">
+        <v>442</v>
       </c>
       <c r="B41">
-        <v>136</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="F41" s="28" t="s">
-        <v>438</v>
-      </c>
-      <c r="G41" s="29" t="s">
-        <v>439</v>
-      </c>
-      <c r="H41" s="28" t="s">
-        <v>440</v>
-      </c>
-      <c r="J41" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="K41" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="L41" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="M41" s="23" t="s">
-        <v>445</v>
-      </c>
-      <c r="N41" s="24" t="s">
-        <v>446</v>
+        <v>10003</v>
       </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>108</v>
+        <v>418</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>432</v>
+    <row r="42" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="28" t="s">
+        <v>443</v>
       </c>
       <c r="B42">
-        <v>137</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="F42" s="28" t="s">
-        <v>441</v>
-      </c>
-      <c r="G42" s="29" t="s">
-        <v>442</v>
-      </c>
-      <c r="H42" s="28" t="s">
-        <v>443</v>
-      </c>
-      <c r="J42" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="K42" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="L42" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="M42" s="23" t="s">
-        <v>445</v>
-      </c>
-      <c r="N42" s="24" t="s">
-        <v>446</v>
+        <v>10004</v>
       </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>419</v>
+      </c>
+      <c r="B43">
+        <v>136</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="F43" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="G43" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="H43" s="26" t="s">
+        <v>424</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="L43" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="M43" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="N43" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>430</v>
+      </c>
+      <c r="B44">
+        <v>137</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="F44" s="26" t="s">
+        <v>433</v>
+      </c>
+      <c r="G44" s="27" t="s">
+        <v>434</v>
+      </c>
+      <c r="H44" s="26" t="s">
+        <v>435</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="K44" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="L44" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="M44" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="N44" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="P44" s="2" t="s">
         <v>108</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/source/bin/excel/mail.xlsx
+++ b/source/bin/excel/mail.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190B911E-05C8-482A-86A6-8C3E4A323585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92C0178-3B3F-4DF8-9428-A5745F2D6610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,7 +12,7 @@
     <sheet name="mail_template" sheetId="1" r:id="rId2"/>
     <sheet name="邮件参数" sheetId="7" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="483">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -13180,21 +13180,1766 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Twitch Drops Rewards1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Twitch Drops Rewards2</t>
-  </si>
-  <si>
-    <t>Twitch Drops Rewards3</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>独家报道时间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动奖励</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>獨家報導時間活動獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>感谢参与</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>独家报道时间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动，请查收您的奖励。
+邮件有效期为30天，请注意及时领取。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>感謝參與</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>獨家報導時間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
+イベント「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>独占インタビュー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」の報酬をお送りいたしました。
+これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
+※本メールは受信後、30日で削除されますのでご注意ください。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thank you for participating in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Off-the-Record Exclusive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> event. Please claim your rewards.
+*Upon receiving the mail, it will expire in 30 days. Please claim it in time.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단독취재타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참가해주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작사님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감사의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우편의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유효기간은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Twitch Drop Reward 1</t>
+  </si>
+  <si>
+    <t>Twitch Drops Rewards 1</t>
+  </si>
+  <si>
+    <t>Dear Jyanshi Sama
+Thanks for watching Mahjong Soul on Twitch for 15 minutes. You are eligible to receive the corresponding Twitch Drop rewards. Here are your rewards. Please claim them on time.</t>
+  </si>
+  <si>
+    <t>Twitch Drops Rewards 2</t>
+  </si>
+  <si>
+    <t>Twitch Drop Reward 2</t>
+  </si>
+  <si>
+    <t>Dear Jyanshi Sama
+Thanks for watching Mahjong Soul on Twitch for 30 minutes. You are eligible to receive the corresponding Twitch Drop rewards. Here are your rewards. Please claim them on time.</t>
+  </si>
+  <si>
+    <t>Twitch Drops Rewards 3</t>
+  </si>
+  <si>
+    <t>Twitch Drop Reward 3</t>
+  </si>
+  <si>
+    <t>Dear Jyanshi Sama
+Thanks for watching Mahjong Soul on Twitch for 45 minutes. You are eligible to receive the corresponding Twitch Drop reward. Here is your reward. Please claim it on time.</t>
+  </si>
+  <si>
+    <t>Twitch Drops Rewards 4</t>
+  </si>
+  <si>
+    <t>Twitch Drop Reward 4</t>
+  </si>
+  <si>
+    <t>Dear Jyanshi Sama
+Thanks for watching Mahjong Soul on Twitch for 60 minutes. You are eligible to receive the corresponding Twitch Drop reward. Here is your reward. Please claim it on time.</t>
+  </si>
+  <si>
+    <t>Twitch Drops Rewards 5</t>
+  </si>
+  <si>
+    <t>Twitch Drop Reward 5</t>
+  </si>
+  <si>
+    <t>Dear Jyanshi Sama
+Thanks for watching Mahjong Soul on Twitch for 120 minutes. You are eligible to receive the corresponding Twitch Drop reward. Here is your reward. Please claim it 
+on time.</t>
+  </si>
+  <si>
+    <t>「独占インタビュー」報酬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Off-the-Record Exclusive</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Event Rewards</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단독취재타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑域誓约奖励</t>
+  </si>
+  <si>
+    <t>剑域誓约活动奖励</t>
+  </si>
+  <si>
+    <t>劍域誓約活動獎勵</t>
+  </si>
+  <si>
+    <t>「剣域の誓約」報酬</t>
+  </si>
+  <si>
+    <t>Oath of the Sword Event Rewards</t>
+  </si>
+  <si>
+    <r>
+      <t>검역의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>서약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+  </si>
+  <si>
+    <t>感谢参与剑域誓约活动，请查收您的奖励。
+邮件有效期为30天，请注意及时领取。</t>
+  </si>
+  <si>
+    <t>感謝參與劍域誓約活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+  </si>
+  <si>
+    <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
+イベント「剣域の誓約」の報酬をお送りいたしました。
+これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
+※本メールは受信後、30日で削除されますのでご注意ください。</t>
+  </si>
+  <si>
+    <t>Thank you for participating in the Oath of the Sword event. Please claim your rewards.
+*Upon receiving the mail, it will expire in 30 days. Please claim it in time.</t>
+  </si>
+  <si>
+    <r>
+      <t>검역의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>서약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이벤트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>참가해주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>작사님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>감사의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>담아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>보상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>우편의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>유효기간은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>「青雲の志：勇にゃん伝説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」報酬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sky-High Ambition: The Nyavengers Event Rewards</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청운의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꿈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>용사냥냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파티</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
+イベント「青雲の志：勇にゃん伝説」の報酬をお送りいたしました。
+これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
+※本メールは受信後、30日で削除されますのでご注意ください。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thank you for participating in the Sky-High Ambition: The Nyavengers event. Please claim your rewards.
+*Upon receiving the mail, it will expire in 30 days. Please claim it in time.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청운의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꿈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>용사냥냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파티</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참가해주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작사님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감사의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우편의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유효기간은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="47" x14ac:knownFonts="1">
+  <fonts count="49" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13544,6 +15289,19 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -13693,7 +15451,17 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -14049,7 +15817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
@@ -15597,137 +17365,450 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" s="28" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B40">
         <v>10002</v>
       </c>
+      <c r="D40" t="s">
+        <v>448</v>
+      </c>
+      <c r="E40" t="s">
+        <v>448</v>
+      </c>
+      <c r="F40" t="s">
+        <v>448</v>
+      </c>
+      <c r="G40" t="s">
+        <v>448</v>
+      </c>
+      <c r="H40" t="s">
+        <v>448</v>
+      </c>
+      <c r="J40" t="s">
+        <v>450</v>
+      </c>
+      <c r="K40" t="s">
+        <v>450</v>
+      </c>
+      <c r="L40" t="s">
+        <v>450</v>
+      </c>
+      <c r="M40" t="s">
+        <v>450</v>
+      </c>
+      <c r="N40" t="s">
+        <v>450</v>
+      </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>418</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" s="28" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B41">
         <v>10003</v>
       </c>
+      <c r="D41" t="s">
+        <v>452</v>
+      </c>
+      <c r="E41" t="s">
+        <v>452</v>
+      </c>
+      <c r="F41" t="s">
+        <v>452</v>
+      </c>
+      <c r="G41" t="s">
+        <v>452</v>
+      </c>
+      <c r="H41" t="s">
+        <v>452</v>
+      </c>
+      <c r="J41" t="s">
+        <v>453</v>
+      </c>
+      <c r="K41" t="s">
+        <v>453</v>
+      </c>
+      <c r="L41" t="s">
+        <v>453</v>
+      </c>
+      <c r="M41" t="s">
+        <v>453</v>
+      </c>
+      <c r="N41" t="s">
+        <v>453</v>
+      </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>418</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" s="28" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="B42">
         <v>10004</v>
       </c>
+      <c r="D42" t="s">
+        <v>455</v>
+      </c>
+      <c r="E42" t="s">
+        <v>455</v>
+      </c>
+      <c r="F42" t="s">
+        <v>455</v>
+      </c>
+      <c r="G42" t="s">
+        <v>455</v>
+      </c>
+      <c r="H42" t="s">
+        <v>455</v>
+      </c>
+      <c r="J42" t="s">
+        <v>456</v>
+      </c>
+      <c r="K42" t="s">
+        <v>456</v>
+      </c>
+      <c r="L42" t="s">
+        <v>456</v>
+      </c>
+      <c r="M42" t="s">
+        <v>456</v>
+      </c>
+      <c r="N42" t="s">
+        <v>456</v>
+      </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>418</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>419</v>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" s="28" t="s">
+        <v>457</v>
       </c>
       <c r="B43">
-        <v>136</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="F43" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="G43" s="27" t="s">
-        <v>423</v>
-      </c>
-      <c r="H43" s="26" t="s">
-        <v>424</v>
-      </c>
-      <c r="J43" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="K43" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="L43" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="M43" s="23" t="s">
-        <v>428</v>
-      </c>
-      <c r="N43" s="24" t="s">
-        <v>429</v>
+        <v>10005</v>
+      </c>
+      <c r="D43" t="s">
+        <v>458</v>
+      </c>
+      <c r="E43" t="s">
+        <v>458</v>
+      </c>
+      <c r="F43" t="s">
+        <v>458</v>
+      </c>
+      <c r="G43" t="s">
+        <v>458</v>
+      </c>
+      <c r="H43" t="s">
+        <v>458</v>
+      </c>
+      <c r="J43" t="s">
+        <v>459</v>
+      </c>
+      <c r="K43" t="s">
+        <v>459</v>
+      </c>
+      <c r="L43" t="s">
+        <v>459</v>
+      </c>
+      <c r="M43" t="s">
+        <v>459</v>
+      </c>
+      <c r="N43" t="s">
+        <v>459</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>430</v>
+    <row r="44" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="28" t="s">
+        <v>460</v>
       </c>
       <c r="B44">
-        <v>137</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="F44" s="26" t="s">
-        <v>433</v>
-      </c>
-      <c r="G44" s="27" t="s">
-        <v>434</v>
-      </c>
-      <c r="H44" s="26" t="s">
-        <v>435</v>
-      </c>
-      <c r="J44" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="K44" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="L44" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="M44" s="23" t="s">
-        <v>428</v>
-      </c>
-      <c r="N44" s="24" t="s">
-        <v>429</v>
+        <v>10006</v>
+      </c>
+      <c r="D44" t="s">
+        <v>461</v>
+      </c>
+      <c r="E44" t="s">
+        <v>461</v>
+      </c>
+      <c r="F44" t="s">
+        <v>461</v>
+      </c>
+      <c r="G44" t="s">
+        <v>461</v>
+      </c>
+      <c r="H44" t="s">
+        <v>461</v>
+      </c>
+      <c r="J44" t="s">
+        <v>462</v>
+      </c>
+      <c r="K44" t="s">
+        <v>462</v>
+      </c>
+      <c r="L44" t="s">
+        <v>462</v>
+      </c>
+      <c r="M44" t="s">
+        <v>462</v>
+      </c>
+      <c r="N44" t="s">
+        <v>462</v>
       </c>
       <c r="O44">
         <v>1</v>
       </c>
       <c r="P44" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>419</v>
+      </c>
+      <c r="B45">
+        <v>136</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="F45" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="G45" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="H45" s="26" t="s">
+        <v>424</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="L45" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="M45" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="N45" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="O45">
+        <v>1</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>430</v>
+      </c>
+      <c r="B46">
+        <v>137</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="F46" s="26" t="s">
+        <v>433</v>
+      </c>
+      <c r="G46" s="27" t="s">
+        <v>434</v>
+      </c>
+      <c r="H46" s="26" t="s">
+        <v>435</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="L46" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="M46" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="N46" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="O46">
+        <v>1</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>363</v>
+      </c>
+      <c r="B47">
+        <v>138</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="F47" t="s">
+        <v>463</v>
+      </c>
+      <c r="G47" t="s">
+        <v>464</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="J47" s="23" t="s">
+        <v>443</v>
+      </c>
+      <c r="K47" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="L47" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="M47" s="23" t="s">
+        <v>446</v>
+      </c>
+      <c r="N47" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="O47">
+        <v>1</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>466</v>
+      </c>
+      <c r="B48">
+        <v>139</v>
+      </c>
+      <c r="D48" t="s">
+        <v>467</v>
+      </c>
+      <c r="E48" t="s">
+        <v>468</v>
+      </c>
+      <c r="F48" t="s">
+        <v>469</v>
+      </c>
+      <c r="G48" t="s">
+        <v>470</v>
+      </c>
+      <c r="H48" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="O48">
+        <v>1</v>
+      </c>
+      <c r="P48" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>224</v>
+      </c>
+      <c r="B49">
+        <v>140</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="G49" t="s">
+        <v>478</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="L49" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="M49" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="N49" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="O49">
+        <v>1</v>
+      </c>
+      <c r="P49" s="2" t="s">
         <v>108</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B1048576">
+  <conditionalFormatting sqref="B1:B47 B49:B1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/source/bin/excel/mail.xlsx
+++ b/source/bin/excel/mail.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92C0178-3B3F-4DF8-9428-A5745F2D6610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A627FA-8CCF-4C40-868E-B90DE07A3908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
     <sheet name="mail_template" sheetId="1" r:id="rId2"/>
     <sheet name="邮件参数" sheetId="7" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029" calcOnSave="0"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -13760,11 +13760,6 @@
     <t>Twitch Drop Reward 5</t>
   </si>
   <si>
-    <t>Dear Jyanshi Sama
-Thanks for watching Mahjong Soul on Twitch for 120 minutes. You are eligible to receive the corresponding Twitch Drop reward. Here is your reward. Please claim it 
-on time.</t>
-  </si>
-  <si>
     <t>「独占インタビュー」報酬</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -14932,6 +14927,11 @@
       </rPr>
       <t>.</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dear Jyanshi Sama
+Thanks for watching Mahjong Soul on Twitch for 120 minutes. You are eligible to receive the corresponding Twitch Drop reward. Here is your reward. Please claim it on time.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -17539,7 +17539,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="86.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
         <v>460</v>
       </c>
@@ -17561,20 +17561,20 @@
       <c r="H44" t="s">
         <v>461</v>
       </c>
-      <c r="J44" t="s">
-        <v>462</v>
-      </c>
-      <c r="K44" t="s">
-        <v>462</v>
-      </c>
-      <c r="L44" t="s">
-        <v>462</v>
-      </c>
-      <c r="M44" t="s">
-        <v>462</v>
-      </c>
-      <c r="N44" t="s">
-        <v>462</v>
+      <c r="J44" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>482</v>
       </c>
       <c r="O44">
         <v>1</v>
@@ -17685,13 +17685,13 @@
         <v>442</v>
       </c>
       <c r="F47" t="s">
+        <v>462</v>
+      </c>
+      <c r="G47" t="s">
         <v>463</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" s="16" t="s">
         <v>464</v>
-      </c>
-      <c r="H47" s="16" t="s">
-        <v>465</v>
       </c>
       <c r="J47" s="23" t="s">
         <v>443</v>
@@ -17717,40 +17717,40 @@
     </row>
     <row r="48" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B48">
         <v>139</v>
       </c>
       <c r="D48" t="s">
+        <v>466</v>
+      </c>
+      <c r="E48" t="s">
         <v>467</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>468</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>469</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" s="19" t="s">
         <v>470</v>
       </c>
-      <c r="H48" s="19" t="s">
+      <c r="J48" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="K48" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="L48" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="L48" s="2" t="s">
+      <c r="M48" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="N48" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="O48">
         <v>1</v>
@@ -17773,13 +17773,13 @@
         <v>227</v>
       </c>
       <c r="F49" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G49" t="s">
         <v>477</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" s="16" t="s">
         <v>478</v>
-      </c>
-      <c r="H49" s="16" t="s">
-        <v>479</v>
       </c>
       <c r="J49" s="10" t="s">
         <v>235</v>
@@ -17788,13 +17788,13 @@
         <v>236</v>
       </c>
       <c r="L49" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="M49" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="M49" s="13" t="s">
+      <c r="N49" s="15" t="s">
         <v>481</v>
-      </c>
-      <c r="N49" s="15" t="s">
-        <v>482</v>
       </c>
       <c r="O49">
         <v>1</v>

--- a/source/bin/excel/mail.xlsx
+++ b/source/bin/excel/mail.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A627FA-8CCF-4C40-868E-B90DE07A3908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4346B5-A15E-4D93-87BA-CA2F710BB109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="795" yWindow="600" windowWidth="19920" windowHeight="14835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="501">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -14934,12 +14934,1155 @@
 Thanks for watching Mahjong Soul on Twitch for 120 minutes. You are eligible to receive the corresponding Twitch Drop reward. Here is your reward. Please claim it on time.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>传说之夜再临</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传说之夜·再临活动奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>傳説之夜·再臨活動獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「伝説の夜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>再臨」報酬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Night of Legends: Shadows Reborn Event Rewards</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>전설의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>밤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전설의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>밤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이벤트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>참가해주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>작사님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>감사의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>담아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>보상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>우편의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>유효기간은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thank you for participating in The Night of Legends: Shadows Reborn event. Please claim your rewards.
+*Upon receiving the mail, it will expire in 30 days. Please claim it in time.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
+イベント「伝説の夜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>再臨」の報酬をお送りいたしました。
+これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
+※本メールは受信後、30日で削除されますのでご注意ください。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感謝參與傳説之夜·再臨活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感谢参与传说之夜·再临活动，请查收您的奖励。
+邮件有效期为30天，请注意及时领取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青云之志限时奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「青雲の志：失われた聖餌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」報酬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sky-High Ambition: Finders Kitties Event Rewards</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청운의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꿈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냥냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보물찾기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
+イベント「青雲の志：失われた聖餌」の報酬をお送りいたしました。
+これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
+※本メールは受信後、30日で削除されますのでご注意ください。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thank you for participating in the Sky-High Ambition: Finders Kitties event. Please claim your rewards.
+*Upon receiving the mail, it will expire in 30 days. Please claim it in time.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청운의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꿈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냥냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보물찾기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참가해주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작사님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감사의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우편의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유효기간은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="49" x14ac:knownFonts="1">
+  <fonts count="51" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -15302,6 +16445,21 @@
       <family val="1"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -15376,7 +16534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -15447,11 +16605,35 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -15817,7 +16999,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
@@ -17803,12 +18985,106 @@
         <v>108</v>
       </c>
     </row>
+    <row r="50" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>494</v>
+      </c>
+      <c r="B50">
+        <v>141</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="G50" t="s">
+        <v>496</v>
+      </c>
+      <c r="H50" s="31" t="s">
+        <v>497</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="K50" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="L50" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="M50" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="N50" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="O50">
+        <v>1</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>483</v>
+      </c>
+      <c r="B51">
+        <v>142</v>
+      </c>
+      <c r="D51" t="s">
+        <v>484</v>
+      </c>
+      <c r="E51" t="s">
+        <v>485</v>
+      </c>
+      <c r="F51" t="s">
+        <v>486</v>
+      </c>
+      <c r="G51" t="s">
+        <v>487</v>
+      </c>
+      <c r="H51" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="N51" s="30" t="s">
+        <v>489</v>
+      </c>
+      <c r="O51">
+        <v>1</v>
+      </c>
+      <c r="P51" t="s">
+        <v>292</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B47 B49:B1048576">
+  <conditionalFormatting sqref="B52:B1048576 B1:B47 B49">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B50">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/source/bin/excel/mail.xlsx
+++ b/source/bin/excel/mail.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4346B5-A15E-4D93-87BA-CA2F710BB109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820CA8AF-AA5F-4B74-8B70-1CAC9978484F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="600" windowWidth="19920" windowHeight="14835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="502">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -16075,6 +16075,10 @@
       </rPr>
       <t>.</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投票</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -16613,7 +16617,17 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -16999,7 +17013,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S51"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
@@ -19029,7 +19043,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>483</v>
       </c>
@@ -19071,20 +19085,67 @@
       </c>
       <c r="P51" t="s">
         <v>292</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>501</v>
+      </c>
+      <c r="B52">
+        <v>143</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="F52" t="s">
+        <v>355</v>
+      </c>
+      <c r="G52" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="H52" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="J52" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="K52" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="L52" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="M52" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="N52" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="O52">
+        <v>1</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B52:B1048576 B1:B47 B49">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B50">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="B53:B1048576 B1:B47 B49">
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
+  <conditionalFormatting sqref="B52">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/source/bin/excel/mail.xlsx
+++ b/source/bin/excel/mail.xlsx
@@ -1,28 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820CA8AF-AA5F-4B74-8B70-1CAC9978484F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5CC05CD-B73E-4A49-A6FC-74E11545FD25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
     <sheet name="mail_template" sheetId="1" r:id="rId2"/>
     <sheet name="邮件参数" sheetId="7" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="529">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -16081,12 +16090,1370 @@
     <t>投票</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>海滨快闪店奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>海滨快闪店</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动奖励</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感谢参与海滨快闪店活动，请查收您的奖励。
+邮件有效期为30天，请注意及时领取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感謝參與海濱快閃店活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>海濱快閃店</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活動獎勵</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.8 夏活 Twitch Drop配置</t>
+  </si>
+  <si>
+    <t>Dear Jyanshi Sama
+Thanks for watching Mahjong Soul on Twitch for 15 minutes. You are eligible to receive the corresponding Twitch Drop reward. Here is your reward. Please claim it on time.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dear Jyanshi Sama
+Thanks for watching Mahjong Soul on Twitch for 30 minutes. You are eligible to receive the corresponding Twitch Drop rewards. Here are your rewards. Please claim them on time.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dear Jyanshi Sama
+Thanks for watching Mahjong Soul on Twitch for 60 minutes. You are eligible to receive the corresponding Twitch Drop reward. Here is your reward. Please claim it on time.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dear Jyanshi Sama
+Thanks for watching Mahjong Soul on Twitch for 120 minutes. You are eligible to receive the corresponding Twitch Drop reward. Here is your reward. Please claim it 
+on time.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>海辺の麻雀小屋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」報酬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Beachside Cabana </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Event Rewards</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해변</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팝업스토어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해변</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팝업스토어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참가해주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작사님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감사의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우편의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유효기간은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thank you for participating in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Beachside Cabana</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> event. Please claim your rewards.
+*Upon receiving the mail, it will expire in 30 days. Please claim it in time.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
+イベント「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>海辺の麻雀小屋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」の報酬をお送りいたしました。
+これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
+※本メールは受信後、30日で削除されますのでご注意ください。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7月_翻牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>流火掣风</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动奖励</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流火掣風活動獎勵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「流火御風」報酬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Windborne Flames </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Event Rewards</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바람을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가르는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불꽃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>感谢参与</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>流火掣风</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>活动，请查收您的奖励。
+邮件有效期为30天，请注意及时领取。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感謝參與流火掣風活動，請查收您的獎勵。
+郵件有效期為30天，請注意及時領取。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>いつも「雀魂-じゃんたま-」をお楽しみいただき、誠にありがとうございます。
+イベント「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>流火御風</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」の報酬をお送りいたしました。
+これからも「雀魂-じゃんたま-」をどうぞよろしくお願いします。
+※本メールは受信後、30日で削除されますのでご注意ください。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thank you for participating in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Windborne Flames</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> event. Please claim your rewards.
+*Upon receiving the mail, it will expire in 30 days. Please claim it in time.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바람을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가르는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불꽃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참가해주신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작사님께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감사의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>담아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우편의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유효기간은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="51" x14ac:knownFonts="1">
+  <fonts count="51">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -16617,7 +17984,27 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -16950,7 +18337,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.375" bestFit="1" customWidth="1"/>
@@ -16961,7 +18348,7 @@
     <col min="8" max="8" width="55.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -16978,7 +18365,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -17013,8 +18400,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S52"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:S58"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
@@ -17034,7 +18421,7 @@
     <col min="17" max="19" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -17093,7 +18480,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -17116,7 +18503,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -17169,7 +18556,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19">
       <c r="B4">
         <v>101</v>
       </c>
@@ -17183,7 +18570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19">
       <c r="B5">
         <v>102</v>
       </c>
@@ -17197,7 +18584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19">
       <c r="B6">
         <v>103</v>
       </c>
@@ -17211,7 +18598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19">
       <c r="B7">
         <v>104</v>
       </c>
@@ -17225,7 +18612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="171" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="171">
       <c r="B8">
         <v>105</v>
       </c>
@@ -17245,7 +18632,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="71.25">
       <c r="B9">
         <v>106</v>
       </c>
@@ -17281,7 +18668,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="185.25">
       <c r="B10">
         <v>107</v>
       </c>
@@ -17317,7 +18704,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="71.25">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -17356,7 +18743,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="140.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="140.25">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -17400,7 +18787,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="140.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="140.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -17444,7 +18831,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="85.5">
       <c r="A14" t="s">
         <v>148</v>
       </c>
@@ -17476,7 +18863,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="140.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="140.25">
       <c r="A15" t="s">
         <v>152</v>
       </c>
@@ -17520,7 +18907,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="51">
       <c r="A16" t="s">
         <v>164</v>
       </c>
@@ -17564,7 +18951,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="141" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="141" thickBot="1">
       <c r="A17" t="s">
         <v>175</v>
       </c>
@@ -17608,7 +18995,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="51.75" thickBot="1">
       <c r="A18" t="s">
         <v>185</v>
       </c>
@@ -17652,7 +19039,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" ht="141" thickBot="1">
       <c r="A19" s="8" t="s">
         <v>194</v>
       </c>
@@ -17696,7 +19083,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" ht="52.5" customHeight="1" thickBot="1">
       <c r="A20" t="s">
         <v>202</v>
       </c>
@@ -17740,7 +19127,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="45.75" customHeight="1" thickBot="1">
       <c r="A21" t="s">
         <v>215</v>
       </c>
@@ -17784,7 +19171,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" ht="45.75" customHeight="1" thickBot="1">
       <c r="A22" t="s">
         <v>224</v>
       </c>
@@ -17828,7 +19215,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" ht="45.75" customHeight="1" thickBot="1">
       <c r="A23" t="s">
         <v>225</v>
       </c>
@@ -17872,7 +19259,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" ht="54.75" customHeight="1" thickBot="1">
       <c r="A24" t="s">
         <v>251</v>
       </c>
@@ -17916,7 +19303,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" ht="55.5" customHeight="1" thickBot="1">
       <c r="A25" t="s">
         <v>262</v>
       </c>
@@ -17960,7 +19347,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="54.75" customHeight="1" thickBot="1">
       <c r="A26" t="s">
         <v>273</v>
       </c>
@@ -18005,7 +19392,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="157.5" thickBot="1">
       <c r="A27" t="s">
         <v>285</v>
       </c>
@@ -18049,7 +19436,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="161.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" ht="161.25" thickBot="1">
       <c r="A28" t="s">
         <v>286</v>
       </c>
@@ -18093,7 +19480,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" ht="157.5" thickBot="1">
       <c r="A29" t="s">
         <v>308</v>
       </c>
@@ -18137,7 +19524,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" ht="157.5" thickBot="1">
       <c r="A30" t="s">
         <v>319</v>
       </c>
@@ -18181,7 +19568,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" ht="157.5" thickBot="1">
       <c r="A31" t="s">
         <v>330</v>
       </c>
@@ -18225,7 +19612,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="157.5" thickBot="1">
       <c r="A32" t="s">
         <v>341</v>
       </c>
@@ -18269,7 +19656,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" ht="157.5" thickBot="1">
       <c r="A33" t="s">
         <v>352</v>
       </c>
@@ -18313,7 +19700,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" ht="157.5" thickBot="1">
       <c r="A34" t="s">
         <v>363</v>
       </c>
@@ -18357,7 +19744,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" ht="157.5" thickBot="1">
       <c r="A35" t="s">
         <v>374</v>
       </c>
@@ -18401,7 +19788,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" ht="157.5" thickBot="1">
       <c r="A36" t="s">
         <v>390</v>
       </c>
@@ -18445,7 +19832,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" ht="157.5" thickBot="1">
       <c r="A37" t="s">
         <v>388</v>
       </c>
@@ -18489,7 +19876,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" ht="157.5" thickBot="1">
       <c r="A38" t="s">
         <v>407</v>
       </c>
@@ -18533,7 +19920,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" ht="71.25">
       <c r="A39" s="28" t="s">
         <v>436</v>
       </c>
@@ -18559,7 +19946,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16">
       <c r="A40" s="28" t="s">
         <v>449</v>
       </c>
@@ -18603,7 +19990,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16">
       <c r="A41" s="28" t="s">
         <v>451</v>
       </c>
@@ -18647,7 +20034,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16">
       <c r="A42" s="28" t="s">
         <v>454</v>
       </c>
@@ -18691,7 +20078,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" ht="71.25">
       <c r="A43" s="28" t="s">
         <v>457</v>
       </c>
@@ -18713,8 +20100,8 @@
       <c r="H43" t="s">
         <v>458</v>
       </c>
-      <c r="J43" t="s">
-        <v>459</v>
+      <c r="J43" s="2" t="s">
+        <v>510</v>
       </c>
       <c r="K43" t="s">
         <v>459</v>
@@ -18735,7 +20122,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="86.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="85.5">
       <c r="A44" s="28" t="s">
         <v>460</v>
       </c>
@@ -18779,218 +20166,218 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>419</v>
+    <row r="45" spans="1:16" ht="85.5">
+      <c r="A45" s="28" t="s">
+        <v>507</v>
       </c>
       <c r="B45">
-        <v>136</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="F45" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="G45" s="27" t="s">
-        <v>423</v>
-      </c>
-      <c r="H45" s="26" t="s">
-        <v>424</v>
-      </c>
-      <c r="J45" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="K45" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="L45" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="M45" s="23" t="s">
-        <v>428</v>
-      </c>
-      <c r="N45" s="24" t="s">
-        <v>429</v>
+        <v>10007</v>
+      </c>
+      <c r="D45" t="s">
+        <v>448</v>
+      </c>
+      <c r="E45" t="s">
+        <v>448</v>
+      </c>
+      <c r="F45" t="s">
+        <v>448</v>
+      </c>
+      <c r="G45" t="s">
+        <v>448</v>
+      </c>
+      <c r="H45" t="s">
+        <v>448</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>508</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>430</v>
+    <row r="46" spans="1:16" ht="85.5">
+      <c r="A46" s="28" t="s">
+        <v>507</v>
       </c>
       <c r="B46">
-        <v>137</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="F46" s="26" t="s">
-        <v>433</v>
-      </c>
-      <c r="G46" s="27" t="s">
-        <v>434</v>
-      </c>
-      <c r="H46" s="26" t="s">
-        <v>435</v>
-      </c>
-      <c r="J46" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="K46" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="L46" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="M46" s="23" t="s">
-        <v>428</v>
-      </c>
-      <c r="N46" s="24" t="s">
-        <v>429</v>
+        <v>10008</v>
+      </c>
+      <c r="D46" t="s">
+        <v>452</v>
+      </c>
+      <c r="E46" t="s">
+        <v>452</v>
+      </c>
+      <c r="F46" t="s">
+        <v>452</v>
+      </c>
+      <c r="G46" t="s">
+        <v>452</v>
+      </c>
+      <c r="H46" t="s">
+        <v>452</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>509</v>
       </c>
       <c r="O46">
         <v>1</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>363</v>
+    <row r="47" spans="1:16" ht="85.5">
+      <c r="A47" s="28" t="s">
+        <v>507</v>
       </c>
       <c r="B47">
-        <v>138</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="E47" s="17" t="s">
-        <v>442</v>
+        <v>10009</v>
+      </c>
+      <c r="D47" t="s">
+        <v>455</v>
+      </c>
+      <c r="E47" t="s">
+        <v>455</v>
       </c>
       <c r="F47" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="G47" t="s">
-        <v>463</v>
-      </c>
-      <c r="H47" s="16" t="s">
-        <v>464</v>
-      </c>
-      <c r="J47" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="K47" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="L47" s="23" t="s">
-        <v>445</v>
-      </c>
-      <c r="M47" s="23" t="s">
-        <v>446</v>
-      </c>
-      <c r="N47" s="24" t="s">
-        <v>447</v>
+        <v>455</v>
+      </c>
+      <c r="H47" t="s">
+        <v>455</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>510</v>
       </c>
       <c r="O47">
         <v>1</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>465</v>
+    <row r="48" spans="1:16" ht="86.25" thickBot="1">
+      <c r="A48" s="28" t="s">
+        <v>507</v>
       </c>
       <c r="B48">
-        <v>139</v>
+        <v>10010</v>
       </c>
       <c r="D48" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="E48" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="F48" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="G48" t="s">
-        <v>469</v>
-      </c>
-      <c r="H48" s="19" t="s">
-        <v>470</v>
+        <v>458</v>
+      </c>
+      <c r="H48" t="s">
+        <v>458</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>471</v>
+        <v>511</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>472</v>
+        <v>511</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>473</v>
+        <v>511</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>475</v>
+        <v>511</v>
       </c>
       <c r="O48">
         <v>1</v>
       </c>
-      <c r="P48" t="s">
-        <v>292</v>
+      <c r="P48" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" ht="157.5" thickBot="1">
       <c r="A49" t="s">
-        <v>224</v>
+        <v>419</v>
       </c>
       <c r="B49">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>226</v>
+        <v>420</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="G49" t="s">
-        <v>477</v>
-      </c>
-      <c r="H49" s="16" t="s">
-        <v>478</v>
+        <v>421</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="G49" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="H49" s="26" t="s">
+        <v>424</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>235</v>
+        <v>425</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="L49" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="M49" s="13" t="s">
-        <v>480</v>
-      </c>
-      <c r="N49" s="15" t="s">
-        <v>481</v>
+        <v>426</v>
+      </c>
+      <c r="L49" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="M49" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="N49" s="24" t="s">
+        <v>429</v>
       </c>
       <c r="O49">
         <v>1</v>
@@ -18999,42 +20386,42 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" ht="157.5" thickBot="1">
       <c r="A50" t="s">
-        <v>494</v>
+        <v>430</v>
       </c>
       <c r="B50">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>226</v>
+        <v>431</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="G50" t="s">
-        <v>496</v>
-      </c>
-      <c r="H50" s="31" t="s">
-        <v>497</v>
+        <v>432</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>433</v>
+      </c>
+      <c r="G50" s="27" t="s">
+        <v>434</v>
+      </c>
+      <c r="H50" s="26" t="s">
+        <v>435</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>235</v>
+        <v>425</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="L50" s="13" t="s">
-        <v>498</v>
-      </c>
-      <c r="M50" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="N50" s="15" t="s">
-        <v>500</v>
+        <v>426</v>
+      </c>
+      <c r="L50" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="M50" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="N50" s="24" t="s">
+        <v>429</v>
       </c>
       <c r="O50">
         <v>1</v>
@@ -19043,110 +20430,380 @@
         <v>108</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" ht="157.5" thickBot="1">
       <c r="A51" t="s">
-        <v>483</v>
+        <v>363</v>
       </c>
       <c r="B51">
-        <v>142</v>
-      </c>
-      <c r="D51" t="s">
-        <v>484</v>
-      </c>
-      <c r="E51" t="s">
-        <v>485</v>
+        <v>138</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>442</v>
       </c>
       <c r="F51" t="s">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="G51" t="s">
-        <v>487</v>
-      </c>
-      <c r="H51" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="N51" s="30" t="s">
-        <v>489</v>
+        <v>463</v>
+      </c>
+      <c r="H51" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="J51" s="23" t="s">
+        <v>443</v>
+      </c>
+      <c r="K51" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="L51" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="M51" s="23" t="s">
+        <v>446</v>
+      </c>
+      <c r="N51" s="24" t="s">
+        <v>447</v>
       </c>
       <c r="O51">
         <v>1</v>
       </c>
-      <c r="P51" t="s">
-        <v>292</v>
+      <c r="P51" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" ht="157.5" thickBot="1">
       <c r="A52" t="s">
-        <v>501</v>
+        <v>465</v>
       </c>
       <c r="B52">
-        <v>143</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>353</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>354</v>
+        <v>139</v>
+      </c>
+      <c r="D52" t="s">
+        <v>466</v>
+      </c>
+      <c r="E52" t="s">
+        <v>467</v>
       </c>
       <c r="F52" t="s">
-        <v>355</v>
-      </c>
-      <c r="G52" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="H52" s="16" t="s">
-        <v>357</v>
-      </c>
-      <c r="J52" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="K52" s="23" t="s">
-        <v>359</v>
-      </c>
-      <c r="L52" s="23" t="s">
-        <v>360</v>
-      </c>
-      <c r="M52" s="23" t="s">
-        <v>361</v>
-      </c>
-      <c r="N52" s="24" t="s">
-        <v>362</v>
+        <v>468</v>
+      </c>
+      <c r="G52" t="s">
+        <v>469</v>
+      </c>
+      <c r="H52" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>475</v>
       </c>
       <c r="O52">
         <v>1</v>
       </c>
-      <c r="P52" s="2" t="s">
+      <c r="P52" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="45.75" customHeight="1" thickBot="1">
+      <c r="A53" t="s">
+        <v>224</v>
+      </c>
+      <c r="B53">
+        <v>140</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G53" t="s">
+        <v>477</v>
+      </c>
+      <c r="H53" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="J53" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="L53" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="M53" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="N53" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="O53">
+        <v>1</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="45.75" customHeight="1" thickBot="1">
+      <c r="A54" t="s">
+        <v>494</v>
+      </c>
+      <c r="B54">
+        <v>141</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="G54" t="s">
+        <v>496</v>
+      </c>
+      <c r="H54" s="31" t="s">
+        <v>497</v>
+      </c>
+      <c r="J54" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="K54" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="L54" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="M54" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="N54" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="O54">
+        <v>1</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="157.5" thickBot="1">
+      <c r="A55" t="s">
+        <v>483</v>
+      </c>
+      <c r="B55">
+        <v>142</v>
+      </c>
+      <c r="D55" t="s">
+        <v>484</v>
+      </c>
+      <c r="E55" t="s">
+        <v>485</v>
+      </c>
+      <c r="F55" t="s">
+        <v>486</v>
+      </c>
+      <c r="G55" t="s">
+        <v>487</v>
+      </c>
+      <c r="H55" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="N55" s="30" t="s">
+        <v>489</v>
+      </c>
+      <c r="O55">
+        <v>1</v>
+      </c>
+      <c r="P55" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="157.5" thickBot="1">
+      <c r="A56" t="s">
+        <v>501</v>
+      </c>
+      <c r="B56">
+        <v>143</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="F56" t="s">
+        <v>355</v>
+      </c>
+      <c r="G56" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="H56" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="J56" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="K56" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="L56" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="M56" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="N56" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="O56">
+        <v>1</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="157.5" thickBot="1">
+      <c r="A57" t="s">
+        <v>502</v>
+      </c>
+      <c r="B57">
+        <v>144</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="F57" t="s">
+        <v>512</v>
+      </c>
+      <c r="G57" s="17" t="s">
+        <v>513</v>
+      </c>
+      <c r="H57" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="L57" s="23" t="s">
+        <v>517</v>
+      </c>
+      <c r="M57" s="23" t="s">
+        <v>516</v>
+      </c>
+      <c r="N57" s="24" t="s">
+        <v>515</v>
+      </c>
+      <c r="O57">
+        <v>1</v>
+      </c>
+      <c r="P57" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="157.5" thickBot="1">
+      <c r="A58" t="s">
+        <v>518</v>
+      </c>
+      <c r="B58">
+        <v>145</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>520</v>
+      </c>
+      <c r="F58" t="s">
+        <v>521</v>
+      </c>
+      <c r="G58" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="H58" s="16" t="s">
+        <v>523</v>
+      </c>
+      <c r="J58" s="23" t="s">
+        <v>524</v>
+      </c>
+      <c r="K58" s="23" t="s">
+        <v>525</v>
+      </c>
+      <c r="L58" s="23" t="s">
+        <v>526</v>
+      </c>
+      <c r="M58" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="N58" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="O58">
+        <v>1</v>
+      </c>
+      <c r="P58" s="2" t="s">
         <v>108</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B53:B1048576 B1:B47 B49">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59:B1048576 B53 B1:B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19156,7 +20813,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B3:N10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="21.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.125" customWidth="1"/>
@@ -19165,7 +20822,7 @@
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:14">
       <c r="B3" t="s">
         <v>22</v>
       </c>
@@ -19185,7 +20842,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:14">
       <c r="B4">
         <v>0</v>
       </c>
@@ -19214,7 +20871,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:14">
       <c r="B5">
         <v>1</v>
       </c>
@@ -19249,7 +20906,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:14">
       <c r="B6">
         <v>2</v>
       </c>
@@ -19283,7 +20940,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:14">
       <c r="I7" t="s">
         <v>59</v>
       </c>
@@ -19297,7 +20954,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:14">
       <c r="I8" t="s">
         <v>64</v>
       </c>
@@ -19311,7 +20968,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:14">
       <c r="I9" t="s">
         <v>68</v>
       </c>
@@ -19331,7 +20988,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:14">
       <c r="I10" t="s">
         <v>74</v>
       </c>
